--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487452_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487452_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2</v>
+        <v>7.7713</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8146</v>
+        <v>4.3592</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3854</v>
+        <v>3.4121</v>
       </c>
       <c r="G2" t="n">
         <v>5.4941</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1363</v>
+        <v>0.4351</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4529</v>
+        <v>0.0917</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3166</v>
+        <v>0.3433</v>
       </c>
       <c r="V2" t="n">
         <v>0.2754</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7311</v>
+        <v>4.4603</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5835</v>
+        <v>1.0454</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1476</v>
+        <v>3.4149</v>
       </c>
       <c r="G3" t="n">
         <v>3.5962</v>
@@ -688,13 +688,13 @@
         <v>2.7419</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3676</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0304</v>
+        <v>0.4923</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.3955</v>
       </c>
       <c r="V3" t="n">
         <v>1.159</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1873</v>
+        <v>2.662</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0239</v>
+        <v>0.5521</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1634</v>
+        <v>2.11</v>
       </c>
       <c r="G4" t="n">
         <v>2.4919</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4209</v>
+        <v>0.0538</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3805</v>
+        <v>0.1476</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0403</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2754</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4267</v>
+        <v>1.3141</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1029</v>
+        <v>-1.1888</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5296</v>
+        <v>2.5029</v>
       </c>
       <c r="G5" t="n">
         <v>4.9879</v>
@@ -844,13 +844,13 @@
         <v>2.7419</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3386</v>
+        <v>0.226</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5264</v>
+        <v>0.4405</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1878</v>
+        <v>-0.2145</v>
       </c>
       <c r="V5" t="n">
         <v>-1.5495</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>F. CANITROT LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4864</v>
+        <v>0.3323</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.671</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1574</v>
+        <v>0.3323</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5494</v>
+        <v>0.4093</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1949</v>
+        <v>0.4093</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3545</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.712</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7824</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9295</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8374</v>
+        <v>0.4093</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4125</v>
+        <v>0.4093</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4249</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.3502</v>
+        <v>0.1958</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.1128</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7626</v>
+        <v>0.1958</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5614</v>
+        <v>-0.2729</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1204</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.441</v>
+        <v>-0.2729</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2742</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. CANITROT LOPEZ</t>
+          <t>G. RUMSHA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3323</v>
+        <v>-0.0526</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.8373</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3323</v>
+        <v>0.7847</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4093</v>
+        <v>0.368</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4093</v>
+        <v>1.2216</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.8535</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.1421</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0612</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0808</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4093</v>
+        <v>0.226</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4093</v>
+        <v>1.1603</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.9344</v>
       </c>
       <c r="P7" t="n">
         <v>0.1958</v>
@@ -1000,19 +1000,19 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2729</v>
+        <v>0.0494</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.3135</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2729</v>
+        <v>0.3629</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. RUMSHA</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1668</v>
+        <v>-0.2378</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0584</v>
+        <v>-2.0209</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8915999999999999</v>
+        <v>1.7831</v>
       </c>
       <c r="G8" t="n">
-        <v>0.368</v>
+        <v>2.5494</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2216</v>
+        <v>1.1949</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8535</v>
+        <v>1.3545</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1421</v>
+        <v>1.712</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0612</v>
+        <v>0.7824</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0808</v>
+        <v>0.9295</v>
       </c>
       <c r="M8" t="n">
-        <v>0.226</v>
+        <v>0.8374</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1603</v>
+        <v>0.4125</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9344</v>
+        <v>0.4249</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1958</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-4.1128</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1958</v>
+        <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0648</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5346</v>
+        <v>0.7705</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4698</v>
+        <v>0.0668</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6659</v>
+        <v>-1.2742</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6659</v>
+        <v>-0.3905</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8641</v>
+        <v>-0.5747</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8556</v>
+        <v>-2.7532</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9914</v>
+        <v>2.1785</v>
       </c>
       <c r="G9" t="n">
         <v>0.7914</v>
@@ -1156,13 +1156,13 @@
         <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2638</v>
+        <v>-0.9744</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3564</v>
+        <v>-0.2541</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9074</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9961</v>
+        <v>-0.7285</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4432</v>
+        <v>-3.4697</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4471</v>
+        <v>2.7412</v>
       </c>
       <c r="G10" t="n">
         <v>0.0439</v>
@@ -1234,13 +1234,13 @@
         <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8073</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.09</v>
+        <v>-0.1165</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7173</v>
+        <v>-0.4233</v>
       </c>
       <c r="V10" t="n">
         <v>0.5507</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6167</v>
+        <v>-1.0932</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4129</v>
+        <v>0.2176</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2039</v>
+        <v>-1.3108</v>
       </c>
       <c r="G11" t="n">
         <v>1.0354</v>
@@ -1312,13 +1312,13 @@
         <v>0.9792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0231</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.517</v>
+        <v>0.1135</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4939</v>
+        <v>0.387</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4332</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5881</v>
+        <v>-2.5333</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0963</v>
+        <v>-1.9345</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4918</v>
+        <v>-0.5987</v>
       </c>
       <c r="G12" t="n">
         <v>0.3195</v>
@@ -1390,13 +1390,13 @@
         <v>0.1958</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0716</v>
+        <v>0.1265</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1782</v>
+        <v>-0.0165</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2498</v>
+        <v>0.1429</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2166</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.132</v>
+        <v>11.3199</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.218299999999999</v>
+        <v>-6.0301</v>
       </c>
       <c r="F13" t="n">
-        <v>17.3501</v>
+        <v>17.3502</v>
       </c>
       <c r="G13" t="n">
         <v>22.087</v>
@@ -1468,13 +1468,13 @@
         <v>14.6884</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6499</v>
+        <v>0.5380999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1675999999999999</v>
+        <v>1.3555</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8173999999999999</v>
+        <v>-0.8174000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-5.4297</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>M. CACHOPAS GIL PRATES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0489</v>
+        <v>3.1866</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4709</v>
+        <v>1.1009</v>
       </c>
       <c r="F14" t="n">
-        <v>2.578</v>
+        <v>2.0857</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.7781</v>
+        <v>-0.0422</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.9453</v>
+        <v>2.7012</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8328</v>
+        <v>-2.7434</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.3791</v>
+        <v>0.1246</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.2683</v>
+        <v>2.0857</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8891</v>
+        <v>-1.9611</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3989</v>
+        <v>-0.1668</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.677</v>
+        <v>0.6156</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7219</v>
+        <v>-0.7823</v>
       </c>
       <c r="P14" t="n">
-        <v>3.3294</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.5875</v>
+        <v>-3.1336</v>
       </c>
       <c r="R14" t="n">
-        <v>3.917</v>
+        <v>1.9585</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2234</v>
+        <v>-0.2448</v>
       </c>
       <c r="T14" t="n">
-        <v>4.1622</v>
+        <v>-0.1482</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0612</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2742</v>
+        <v>4.6486</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2754</v>
+        <v>4.2581</v>
       </c>
       <c r="X14" t="n">
-        <v>0.9988</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. CACHOPAS GIL PRATES</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4822</v>
+        <v>1.5929</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5893</v>
+        <v>-1.3945</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8929</v>
+        <v>2.9874</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0422</v>
+        <v>-4.7781</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7012</v>
+        <v>-3.9453</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.7434</v>
+        <v>-0.8328</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1246</v>
+        <v>-2.3791</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0857</v>
+        <v>-3.2683</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.9611</v>
+        <v>0.8891</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1668</v>
+        <v>-2.3989</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6156</v>
+        <v>-0.677</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7823</v>
+        <v>-1.7219</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1751</v>
+        <v>3.3294</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.1336</v>
+        <v>-0.5875</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9585</v>
+        <v>3.917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9492</v>
+        <v>1.7673</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6599</v>
+        <v>1.2968</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2893</v>
+        <v>0.4705</v>
       </c>
       <c r="V15" t="n">
-        <v>4.6486</v>
+        <v>1.2742</v>
       </c>
       <c r="W15" t="n">
-        <v>4.2581</v>
+        <v>0.2754</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3905</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5288</v>
+        <v>0.8137</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9008</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4296</v>
+        <v>1.5098</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2069</v>
@@ -1702,13 +1702,13 @@
         <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2435</v>
+        <v>0.0413</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2794</v>
+        <v>-0.0747</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0358</v>
+        <v>0.116</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2249</v>
+        <v>-1.1936</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0355</v>
+        <v>-2.1379</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8106</v>
+        <v>0.9443</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9550999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>0.5875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5931</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.504</v>
+        <v>0.4017</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0891</v>
+        <v>0.2228</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2754</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6041</v>
+        <v>-1.3091</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8784</v>
+        <v>-0.776</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7257</v>
+        <v>-0.533</v>
       </c>
       <c r="G18" t="n">
         <v>-2.922</v>
@@ -1858,13 +1858,13 @@
         <v>2.546</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4275</v>
+        <v>-0.1325</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3758</v>
+        <v>-0.2735</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0517</v>
+        <v>0.141</v>
       </c>
       <c r="V18" t="n">
         <v>1.5495</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7256</v>
+        <v>-1.756</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.9326</v>
+        <v>-3.728</v>
       </c>
       <c r="F19" t="n">
-        <v>2.207</v>
+        <v>1.972</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7707</v>
@@ -1936,13 +1936,13 @@
         <v>3.3294</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2201</v>
+        <v>0.1898</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1911</v>
+        <v>0.0135</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4113</v>
+        <v>0.1763</v>
       </c>
       <c r="V19" t="n">
         <v>0.6083</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5634</v>
+        <v>-2.6811</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9923</v>
+        <v>-3.276</v>
       </c>
       <c r="F20" t="n">
-        <v>0.429</v>
+        <v>0.5949</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0834</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2254</v>
+        <v>0.6569</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6358</v>
+        <v>0.0806</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4104</v>
+        <v>0.5764</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2754</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ PILLADO</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9675</v>
+        <v>-3.1483</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3207</v>
+        <v>-4.1219</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6468</v>
+        <v>0.9736</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.3324</v>
+        <v>-4.9963</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3165</v>
+        <v>-5.3248</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0159</v>
+        <v>0.3285</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5773</v>
+        <v>-3.0744</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.026</v>
+        <v>-4.9883</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5514</v>
+        <v>1.914</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7551</v>
+        <v>-1.9219</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2905</v>
+        <v>-0.3364</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4646</v>
+        <v>-1.5855</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3709</v>
+        <v>3.5253</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.3917</v>
+        <v>-0.5875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7626</v>
+        <v>4.1128</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7306</v>
+        <v>0.1476</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3517</v>
+        <v>-0.127</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3789</v>
+        <v>0.2747</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2754</v>
+        <v>-1.8249</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>J. FERNANDEZ PILLADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1064</v>
+        <v>-3.5904</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.3499</v>
+        <v>-2.3207</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2435</v>
+        <v>-1.2697</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.9963</v>
+        <v>-4.3324</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.3248</v>
+        <v>-2.3165</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3285</v>
+        <v>-2.0159</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.0744</v>
+        <v>-1.5773</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.9883</v>
+        <v>-1.026</v>
       </c>
       <c r="L22" t="n">
-        <v>1.914</v>
+        <v>-0.5514</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9219</v>
+        <v>-2.7551</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3364</v>
+        <v>-1.2905</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5855</v>
+        <v>-1.4646</v>
       </c>
       <c r="P22" t="n">
-        <v>3.5253</v>
+        <v>1.3709</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.5875</v>
+        <v>-0.3917</v>
       </c>
       <c r="R22" t="n">
-        <v>4.1128</v>
+        <v>1.7626</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8105</v>
+        <v>-0.3536</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3551</v>
+        <v>-0.3517</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4554</v>
+        <v>-0.0019</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8249</v>
+        <v>-0.2754</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.492</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.132</v>
+        <v>-8.0853</v>
       </c>
       <c r="E23" t="n">
-        <v>-17.35</v>
+        <v>-17.3502</v>
       </c>
       <c r="F23" t="n">
-        <v>7.2181</v>
+        <v>9.265000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-22.0871</v>
@@ -2236,10 +2236,10 @@
         <v>-3.0413</v>
       </c>
       <c r="O23" t="n">
-        <v>-9.2659</v>
+        <v>-9.265899999999998</v>
       </c>
       <c r="P23" t="n">
-        <v>5.875400000000001</v>
+        <v>5.8754</v>
       </c>
       <c r="Q23" t="n">
         <v>-14.6886</v>
@@ -2248,22 +2248,22 @@
         <v>20.5639</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6498999999999999</v>
+        <v>2.6965</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8174000000000003</v>
+        <v>0.8175</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1675000000000001</v>
+        <v>1.8792</v>
       </c>
       <c r="V23" t="n">
-        <v>5.429500000000001</v>
+        <v>5.4295</v>
       </c>
       <c r="W23" t="n">
         <v>6.3009</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8713999999999998</v>
+        <v>-0.8713999999999996</v>
       </c>
     </row>
   </sheetData>
